--- a/inputData/Experiments/inputDataEx2_1_2.xlsx
+++ b/inputData/Experiments/inputDataEx2_1_2.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D482D9BB-3A40-44B7-B876-12FC760ED0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564B657B-559A-8242-A3F7-C1DA0085142A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroupsB" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>type</t>
   </si>
@@ -98,7 +99,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -496,12 +497,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -509,7 +510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -525,14 +526,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,7 +547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -563,7 +564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -580,19 +581,19 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="D6" s="1"/>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5">
       <c r="E18" s="4"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:5">
       <c r="D20" s="4"/>
     </row>
   </sheetData>
@@ -604,13 +605,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -630,7 +631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -650,7 +651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -670,7 +671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="13:24">
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -678,7 +679,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="13:24">
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -692,7 +693,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="13:24">
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -706,7 +707,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="13:24">
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -720,7 +721,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="13:24">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -734,7 +735,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="13:24">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -748,7 +749,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="13:24">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -762,7 +763,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="13:24">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -776,7 +777,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="13:24">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -790,7 +791,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="13:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="13:24">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -807,4 +808,212 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA121BEF-876C-A149-9296-25CA4E7A4177}">
+  <dimension ref="A1:X32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>42</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>91</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="13:24">
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="13:24">
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="13:24">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="13:24">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+    </row>
+    <row r="27" spans="13:24">
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="13:24">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="13:24">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+    </row>
+    <row r="30" spans="13:24">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="13:24">
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="13:24">
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>